--- a/docs/manual_test_plan.xlsx
+++ b/docs/manual_test_plan.xlsx
@@ -13175,7 +13175,8 @@
           <t>1. Open Project ▸ Help ▸ Prerequisites and read every row of the Capability prerequisites dialog.
 2. On the media open `docs/INSTALLATION_PREREQUISITES.md` and the README's prerequisites paragraph.
 3. Repeat step 1 on the pack machine after T-INS-05.
-   Expected: The dialog lists six capabilities — Python equations, DLIS import, Spreadsheet plate extraction, Workbook export, Document export, Deck export — each unavailable, each naming the package it needs. No surface says the product has no runtime dependency. On the pack machine the same rows read available with the interpreter path. Dialog and fragment agree row for row. Known gap (SB-INS-004): the manifest is six rows and other Python-backed actions exist — the image-conditioning Pillow path is one. Write down every Python-backed action you can find that the dialog does not name; that list is the evidence SB-INS-004 and SB-INS-026 are waiting for.</t>
+   Expected: The dialog lists eleven capabilities — Python equations, DLIS import, Spreadsheet plate extraction, Workbook export, Document export, Deck export, ML models, Core photo imaging, Petrography pore area, Mineral classifier, Picture normalization — each unavailable, each naming the packages it needs. No surface says the product has no runtime dependency. On the pack machine the same rows read available with the interpreter path. Dialog and fragment agree row for row. Petrography pore area and Mineral classifier show owner `UNOWNED`: no PRD chapter carries requirements for them yet, and the row says so rather than borrowing another chapter's name.
+   Update 2026-09-23: the old known gap, six rows while other Python-backed actions existed, is closed. The five missing capabilities were added, and a gated test now fails on any Python runner the dialog does not name. If you still find a Python-backed action missing from the list, that is a Fail. Write down which tool it was.</t>
         </is>
       </c>
     </row>

--- a/docs/manual_test_plan.xlsx
+++ b/docs/manual_test_plan.xlsx
@@ -13251,21 +13251,22 @@
       <c r="G257" s="8" t="inlineStr"/>
       <c r="H257" s="7" t="inlineStr">
         <is>
-          <t>Equation Editor, Data ▸ Import Logs ▾ ▸ Import DLIS…, Plot ▸ Deliverables ▸ Workbook…, report pane Save Word…, Project ▸ Help ▸ Prerequisites</t>
+          <t>Equation Editor, Data ▸ Import Logs ▾ ▸ Import DLIS…, Data ▸ Import / Export ▸ Export DLIS…, Plot ▸ Deliverables ▸ Workbook…, report pane Save Word…, Advance ▸ ML Models…, Project ▸ Help ▸ Prerequisites</t>
         </is>
       </c>
       <c r="I257" s="7" t="inlineStr">
         <is>
-          <t>a machine with a Python 3.10+ that has numpy but NOT scipy, NOT dlisio, NOT xlsxwriter and NOT python-docx (`pip uninstall` them); `SANDIBUMI_PYTHON` pointing at it.</t>
+          <t>a machine with a Python 3.10+ that has numpy but NOT scipy, NOT dlisio, NOT xlsxwriter, NOT python-docx and NOT scikit-learn — remove them in a Command Prompt with `"&lt;that python.exe&gt;" -m pip uninstall scipy dlisio xlsxwriter python-docx scikit-learn`; `SANDIBUMI_PYTHON` pointing at it; a well selected.</t>
         </is>
       </c>
       <c r="J257" s="7" t="inlineStr">
         <is>
           <t>1. In the Equation Editor write an equation that calls `signal.savgol_filter(GR, 11, 2)` and run it.
-2. Data ▸ Import Logs ▾ ▸ Import DLIS….
-3. Plot ▸ Deliverables ▸ Workbook…; then render a report and press Save Word….
-4. Copy the pip command out of one of the messages, run it for python-docx, then open Project ▸ Help ▸ Prerequisites and look for a re-probe control inside the dialog; close and reopen it.
-   Expected: Step 1: the editor is available and the run fails AT the scipy name with a message that names the interpreter path and the pip command — never a bare `NameError`. Step 2: the file dialog and set-name prompt appear, then the import is refused before the file is parsed, naming `dlisio` and the interpreter. Step 3: Workbook… refuses BEFORE its save dialog, naming `xlsxwriter` and the interpreter; Save Word… does NOT — its save dialog opens first and the refusal naming `python-docx` arrives only after a path is picked. That is the gap `sb-ins.md` names for SB-INS-006 ("including the document-deliverable surface"); write it in Notes, it is not a Fail. Step 4: there is no re-probe control inside the dialog (Close is its only button) — that is SB-INS-007's open half, write "no re-probe control" in Notes; after closing and reopening, the Document export row reads available without a restart, because packages are probed on every open. Only the choice of INTERPRETER is fixed for the session: a Python installed on a machine that had none is seen after a restart, not before.</t>
+2. Data ▸ Import Logs ▾ ▸ Import DLIS…; then Data ▸ Import / Export ▸ Export DLIS….
+3. Plot ▸ Deliverables ▸ Workbook…; then, in the report pane, press Save Word…, and separately set the batch format to as Word and press the batch export.
+4. Advance ▸ ML Models…, pick any features, a target and a well, and run it.
+5. Copy the install command out of the Save Word… message and run it in a Command Prompt (not PowerShell, which needs `&amp;` in front of a quoted program). Open Project ▸ Help ▸ Prerequisites and press Check again.
+   Expected: Step 1: the editor is available and the run fails AT the scipy name with a message that names the interpreter path and the command `"&lt;that python.exe&gt;" -m pip install scipy` — never a bare `NameError`, never a bare `pip install`. Step 2: for the import, the file dialog and set-name prompt appear, then the import is refused before the file is parsed, naming `dlisio`, the interpreter and the command — that order is the chapter's own bar for an import (SB-INS-T08); Export DLIS… refuses in a dialog BEFORE its save dialog opens. Step 3: Workbook…, Save Word… and the batch Word export each refuse BEFORE any save or folder dialog opens, naming the missing package (`xlsxwriter`, then `python-docx`), the interpreter and the command, and the command names only that package (pip may still fetch that package's own dependencies). Step 4: the run is refused before the run-custody form opens, with nothing queued and no curves written, naming `scikit-learn` (and `joblib` if that is missing too), the interpreter and the command. Step 5: the dialog shows Checking the session runtime… and then Document export — Available, without a restart. Every install command in this test starts with the quoted interpreter path and `-m pip install`. Only the choice of INTERPRETER is fixed for the session: on a machine that had no Python at all, the dialog says a Python installed since is found at the next start, and a restart is what finds it.</t>
         </is>
       </c>
     </row>
